--- a/00_Data/Metadata/DF_EOF_Crop.xlsx
+++ b/00_Data/Metadata/DF_EOF_Crop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ealbright2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwprod-my.sharepoint.com/personal/zchen2545_wisc_edu/Documents/Research/Discovery Farms/DF Runoff Generation/Github repo/DF_runoff/00_Data/Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C11293-868A-49D8-8249-546F517F29BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{54C11293-868A-49D8-8249-546F517F29BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EDA7459-2843-4A16-ABA8-D6E376E2FD00}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -670,13 +670,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H510"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.453125" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" customWidth="1"/>
-    <col min="5" max="8" width="18.81640625" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" customWidth="1"/>
+    <col min="6" max="8" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
